--- a/src/views/game/zlzq/cardList/laowangCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/laowangCard/z_level.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11790" windowHeight="10800" activeTab="2"/>
+    <workbookView windowWidth="10290" windowHeight="11040" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="蛮石" sheetId="6" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="77">
   <si>
     <t>名称</t>
   </si>
@@ -48,7 +48,13 @@
     <t>蓄力射手</t>
   </si>
   <si>
-    <t>势如破竹</t>
+    <t>势如破竹1</t>
+  </si>
+  <si>
+    <t>势如破竹2</t>
+  </si>
+  <si>
+    <t>旷野猎手</t>
   </si>
   <si>
     <t>强行捕猎</t>
@@ -60,19 +66,16 @@
     <t>蓝色卡等：</t>
   </si>
   <si>
-    <t>无畏猎户</t>
-  </si>
-  <si>
-    <t>圣兽祭师</t>
+    <t>暴怒野人</t>
+  </si>
+  <si>
+    <t>诱敌草人</t>
   </si>
   <si>
     <t>活力仙人掌</t>
   </si>
   <si>
-    <t>飞斧狂人1</t>
-  </si>
-  <si>
-    <t>飞斧狂人2</t>
+    <t>飞斧狂人</t>
   </si>
   <si>
     <t>石斧头领</t>
@@ -84,7 +87,7 @@
     <t>紫色卡等：</t>
   </si>
   <si>
-    <t>鸵鸟王·霍利</t>
+    <t>旷野游侠·大羽</t>
   </si>
   <si>
     <t>比尔&amp;比利</t>
@@ -105,7 +108,7 @@
     <t>蛮石卡等：</t>
   </si>
   <si>
-    <t>落雷击</t>
+    <t>热火冲锋</t>
   </si>
   <si>
     <t>爆燃邪鬼</t>
@@ -117,7 +120,13 @@
     <t>腐化甲蛾</t>
   </si>
   <si>
-    <t>觅食大嘴兽</t>
+    <t>狂暴炎球</t>
+  </si>
+  <si>
+    <t>烈焰风暴</t>
+  </si>
+  <si>
+    <t>碎颅魔</t>
   </si>
   <si>
     <t>铸甲熔岩魔</t>
@@ -126,9 +135,15 @@
     <t>绝望镰魔</t>
   </si>
   <si>
+    <t>符文·致命甲壳</t>
+  </si>
+  <si>
     <t>岩浆球</t>
   </si>
   <si>
+    <t>破卵而出</t>
+  </si>
+  <si>
     <t>灼神双炎</t>
   </si>
   <si>
@@ -156,22 +171,19 @@
     <t>炼狱卡等：</t>
   </si>
   <si>
-    <t>飓风术</t>
-  </si>
-  <si>
     <t>太极剑法</t>
   </si>
   <si>
-    <t>长耳庄巧姑</t>
-  </si>
-  <si>
-    <t>明月心</t>
-  </si>
-  <si>
     <t>执剑道者</t>
   </si>
   <si>
-    <t>连击</t>
+    <t>龟族僧人</t>
+  </si>
+  <si>
+    <t>连击1</t>
+  </si>
+  <si>
+    <t>连击2</t>
   </si>
   <si>
     <t>叶幻师</t>
@@ -180,13 +192,19 @@
     <t>铁山靠</t>
   </si>
   <si>
-    <t>茁壮生长</t>
+    <t>符文·疾风图腾1</t>
+  </si>
+  <si>
+    <t>符文·疾风图腾2</t>
   </si>
   <si>
     <t>风卷残云</t>
   </si>
   <si>
     <t>驱魔道人</t>
+  </si>
+  <si>
+    <t>扫叶僧</t>
   </si>
   <si>
     <t>御风武者</t>
@@ -1207,7 +1225,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1215,7 +1233,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1226,7 +1244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1234,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1248,7 +1266,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1259,101 +1277,101 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
         <v>4</v>
       </c>
-      <c r="C5" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>20.75</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
-        <v>3</v>
-      </c>
-      <c r="C12" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="C10" s="1">
+        <f>AVERAGE(C2:C7)</f>
+        <v>20.1666666666667</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
@@ -1367,13 +1385,19 @@
         <v>5</v>
       </c>
       <c r="C17" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -1381,26 +1405,20 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C11:C17)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
-        <v>16</v>
+      <c r="C21" s="2">
+        <f>AVERAGE(C13:C18)</f>
+        <v>20.8333333333333</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1408,10 +1426,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1419,7 +1437,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
         <v>20</v>
@@ -1430,16 +1448,22 @@
         <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="A27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="3">
+        <v>7</v>
+      </c>
+      <c r="C27" s="3">
+        <v>20</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
@@ -1447,27 +1471,32 @@
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="3">
-        <f>AVERAGE(C23:C26)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="C30" s="3">
+        <f>AVERAGE(C24:C27)</f>
+        <v>19.75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
-        <v>20.4</v>
+      <c r="B33" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="4">
+        <f>AVERAGE(C2:C7,C13:C18,C24:C27)</f>
+        <v>20.3125</v>
       </c>
     </row>
   </sheetData>
@@ -1479,7 +1508,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1487,7 +1516,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1498,31 +1527,31 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
@@ -1531,101 +1560,101 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>20.25</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1">
+        <f>AVERAGE(C2:C7)</f>
+        <v>21.1666666666667</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="2">
         <v>2</v>
       </c>
-      <c r="C11" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="2">
-        <v>3</v>
-      </c>
-      <c r="C12" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="2">
-        <v>3</v>
-      </c>
       <c r="C13" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
         <v>20</v>
@@ -1633,124 +1662,168 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="2">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="2">
+        <v>4</v>
+      </c>
+      <c r="C19" s="2">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
+      </c>
+      <c r="B20" s="2">
+        <v>5</v>
       </c>
       <c r="C20" s="2">
-        <f>AVERAGE(C11:C17)</f>
-        <v>20.1428571428571</v>
-      </c>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="2">
+        <v>6</v>
+      </c>
+      <c r="C21" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="3">
-        <v>2</v>
-      </c>
-      <c r="C23" s="3">
-        <v>12</v>
-      </c>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="3">
-        <v>3</v>
-      </c>
-      <c r="C24" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3">
-        <v>4</v>
-      </c>
-      <c r="C25" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3">
-        <v>5</v>
-      </c>
-      <c r="C26" s="3">
-        <v>20</v>
+      <c r="A24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="2">
+        <f>AVERAGE(C13:C21)</f>
+        <v>20.8888888888889</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C27" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+      <c r="A28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="3">
+        <v>3</v>
+      </c>
+      <c r="C28" s="3">
+        <v>22</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
+      <c r="A29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="3">
+        <v>4</v>
+      </c>
+      <c r="C29" s="3">
+        <v>22</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="3">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3">
         <v>21</v>
       </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C23:C27)</f>
-        <v>18.6</v>
-      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="3">
+        <v>6</v>
+      </c>
+      <c r="C31" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C5,C11:C17,C23:C27)</f>
-        <v>19.6875</v>
+      <c r="C34" s="3">
+        <f>AVERAGE(C27:C31)</f>
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="4">
+        <f>AVERAGE(C2:C7,C13:C21,C27:C31)</f>
+        <v>20.6</v>
       </c>
     </row>
   </sheetData>
@@ -1770,7 +1843,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1781,9 +1854,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1792,153 +1865,153 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B11" s="1">
         <v>4</v>
       </c>
       <c r="C11" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="1">
-        <v>4</v>
-      </c>
-      <c r="C12" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="1">
-        <f>AVERAGE(C2:C12)</f>
-        <v>16.1818181818182</v>
-      </c>
-      <c r="D15" s="2"/>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1">
+        <f>AVERAGE(C2:C11)</f>
+        <v>15.9</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="2">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B18" s="2">
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -1949,7 +2022,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B20" s="2">
         <v>4</v>
@@ -1960,13 +2033,13 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B21" s="2">
         <v>5</v>
       </c>
       <c r="C21" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1981,25 +2054,25 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2">
-        <f>AVERAGE(C18:C21)</f>
-        <v>17.25</v>
+        <f>AVERAGE(C17:C21)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B27" s="3">
         <v>4</v>
       </c>
       <c r="C27" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2014,26 +2087,26 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C30" s="3">
-        <f>AVERAGE(C27:C27)</f>
-        <v>17</v>
+        <f>AVERAGE(C27)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C33" s="4">
-        <f>AVERAGE(C2:C12,C18:C21,C27:C27)</f>
-        <v>16.5</v>
+        <f>AVERAGE(C2:C11,C17:C21,C27:C27)</f>
+        <v>15.4375</v>
       </c>
     </row>
   </sheetData>
@@ -2053,7 +2126,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2064,9 +2137,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -2075,9 +2148,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -2086,9 +2159,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2097,9 +2170,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -2108,9 +2181,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -2119,9 +2192,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -2130,9 +2203,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -2141,9 +2214,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2152,9 +2225,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B10" s="1">
         <v>5</v>
@@ -2163,22 +2236,22 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1">
         <f>AVERAGE(C2:C10)</f>
@@ -2186,9 +2259,9 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -2199,7 +2272,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
@@ -2210,7 +2283,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B18" s="2">
         <v>2</v>
@@ -2221,7 +2294,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -2232,7 +2305,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
@@ -2253,10 +2326,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C16:C20)</f>
@@ -2265,7 +2338,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
@@ -2286,10 +2359,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C26:C26)</f>
@@ -2298,10 +2371,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C10,C16:C20,C26:C26)</f>
@@ -2312,7 +2385,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C13 C32" formulaRange="1"/>
+    <ignoredError sqref="C32 C13" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/views/game/zlzq/cardList/laowangCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/laowangCard/z_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10290" windowHeight="11040" activeTab="2"/>
+    <workbookView windowWidth="11910" windowHeight="11745" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="蛮石" sheetId="6" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="71">
   <si>
     <t>名称</t>
   </si>
@@ -42,21 +42,18 @@
     <t>卡等</t>
   </si>
   <si>
-    <t>愚笨鲸头鹅</t>
-  </si>
-  <si>
     <t>蓄力射手</t>
   </si>
   <si>
-    <t>势如破竹1</t>
-  </si>
-  <si>
-    <t>势如破竹2</t>
+    <t>势如破竹</t>
   </si>
   <si>
     <t>旷野猎手</t>
   </si>
   <si>
+    <t>天降碎石</t>
+  </si>
+  <si>
     <t>强行捕猎</t>
   </si>
   <si>
@@ -66,15 +63,15 @@
     <t>蓝色卡等：</t>
   </si>
   <si>
+    <t>疯狂祭师</t>
+  </si>
+  <si>
+    <t>诱敌草人</t>
+  </si>
+  <si>
     <t>暴怒野人</t>
   </si>
   <si>
-    <t>诱敌草人</t>
-  </si>
-  <si>
-    <t>活力仙人掌</t>
-  </si>
-  <si>
     <t>飞斧狂人</t>
   </si>
   <si>
@@ -108,42 +105,30 @@
     <t>蛮石卡等：</t>
   </si>
   <si>
-    <t>热火冲锋</t>
-  </si>
-  <si>
     <t>爆燃邪鬼</t>
   </si>
   <si>
-    <t>无面狂奔者</t>
-  </si>
-  <si>
     <t>腐化甲蛾</t>
   </si>
   <si>
     <t>狂暴炎球</t>
   </si>
   <si>
-    <t>烈焰风暴</t>
-  </si>
-  <si>
-    <t>碎颅魔</t>
-  </si>
-  <si>
     <t>铸甲熔岩魔</t>
   </si>
   <si>
     <t>绝望镰魔</t>
   </si>
   <si>
+    <t>破卵而出</t>
+  </si>
+  <si>
     <t>符文·致命甲壳</t>
   </si>
   <si>
     <t>岩浆球</t>
   </si>
   <si>
-    <t>破卵而出</t>
-  </si>
-  <si>
     <t>灼神双炎</t>
   </si>
   <si>
@@ -174,6 +159,9 @@
     <t>太极剑法</t>
   </si>
   <si>
+    <t>飓风术</t>
+  </si>
+  <si>
     <t>执剑道者</t>
   </si>
   <si>
@@ -186,16 +174,10 @@
     <t>连击2</t>
   </si>
   <si>
-    <t>叶幻师</t>
-  </si>
-  <si>
     <t>铁山靠</t>
   </si>
   <si>
-    <t>符文·疾风图腾1</t>
-  </si>
-  <si>
-    <t>符文·疾风图腾2</t>
+    <t>符文·疾风图腾</t>
   </si>
   <si>
     <t>风卷残云</t>
@@ -204,9 +186,6 @@
     <t>驱魔道人</t>
   </si>
   <si>
-    <t>扫叶僧</t>
-  </si>
-  <si>
     <t>御风武者</t>
   </si>
   <si>
@@ -217,6 +196,9 @@
   </si>
   <si>
     <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
   </si>
   <si>
     <t>禅意卡等：</t>
@@ -1225,7 +1207,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1249,10 +1231,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1274,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1282,7 +1264,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
         <v>22</v>
@@ -1293,22 +1275,16 @@
         <v>7</v>
       </c>
       <c r="B6" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1">
-        <v>20</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1"/>
@@ -1316,22 +1292,28 @@
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>21.2</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>20.1666666666667</v>
-      </c>
-      <c r="D10" s="2"/>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
@@ -1341,7 +1323,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1360,10 +1342,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1371,7 +1353,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
@@ -1389,15 +1371,9 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2">
-        <v>22</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -1405,20 +1381,26 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="A20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C12:C17)</f>
+        <v>21.1666666666667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C13:C18)</f>
-        <v>20.8333333333333</v>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1426,10 +1408,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1437,10 +1419,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1448,22 +1430,16 @@
         <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" s="3">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="3">
-        <v>7</v>
-      </c>
-      <c r="C27" s="3">
-        <v>20</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
@@ -1471,32 +1447,27 @@
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="A29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C23:C26)</f>
+        <v>20.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C24:C27)</f>
-        <v>19.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C7,C13:C18,C24:C27)</f>
-        <v>20.3125</v>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C6,C12:C17,C23:C26)</f>
+        <v>20.9333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1506,333 +1477,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="1">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="1">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>21.1666666666667</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="2">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="2">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="2">
-        <v>3</v>
-      </c>
-      <c r="C17" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="2">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="2">
-        <v>4</v>
-      </c>
-      <c r="C19" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="2">
-        <v>5</v>
-      </c>
-      <c r="C20" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="2">
-        <v>6</v>
-      </c>
-      <c r="C21" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="2">
-        <f>AVERAGE(C13:C21)</f>
-        <v>20.8888888888889</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="3">
-        <v>2</v>
-      </c>
-      <c r="C27" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="3">
-        <v>3</v>
-      </c>
-      <c r="C28" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="3">
-        <v>4</v>
-      </c>
-      <c r="C29" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="3">
-        <v>5</v>
-      </c>
-      <c r="C30" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="3">
-        <v>6</v>
-      </c>
-      <c r="C31" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="3">
-        <f>AVERAGE(C27:C31)</f>
-        <v>19.4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" s="4">
-        <f>AVERAGE(C2:C7,C13:C21,C27:C31)</f>
-        <v>20.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D33"/>
@@ -1856,18 +1500,18 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1">
         <v>3</v>
@@ -1878,7 +1522,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
@@ -1888,19 +1532,302 @@
       </c>
     </row>
     <row r="5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>21</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="2">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2">
+        <v>3</v>
+      </c>
+      <c r="C11" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2">
+        <v>3</v>
+      </c>
+      <c r="C12" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="2">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C10:C17)</f>
+        <v>21.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="3">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3">
+        <v>5</v>
+      </c>
+      <c r="C26" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3">
+        <v>6</v>
+      </c>
+      <c r="C27" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="3">
+        <f>AVERAGE(C23:C27)</f>
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="4">
+        <f>AVERAGE(C2:C4,C10:C17,C23:C27)</f>
+        <v>20.625</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1911,18 +1838,18 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -1933,7 +1860,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -1944,25 +1871,19 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="1">
-        <v>4</v>
-      </c>
-      <c r="C11" s="1">
-        <v>12</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1"/>
@@ -1970,29 +1891,35 @@
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1">
-        <f>AVERAGE(C2:C11)</f>
-        <v>15.9</v>
-      </c>
-      <c r="D14" s="2"/>
+      <c r="C13" s="1">
+        <f>AVERAGE(C2:C10)</f>
+        <v>16.2222222222222</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2">
         <v>20</v>
@@ -2000,10 +1927,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" s="2">
         <v>12</v>
@@ -2011,69 +1938,63 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="2">
+        <f>AVERAGE(C16:C19)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="3">
         <v>4</v>
       </c>
-      <c r="C19" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="2">
+      <c r="C25" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="3">
         <v>4</v>
       </c>
-      <c r="C20" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="2">
-        <v>5</v>
-      </c>
-      <c r="C21" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="2">
-        <f>AVERAGE(C17:C21)</f>
+      <c r="C26" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="3">
-        <v>4</v>
-      </c>
-      <c r="C27" s="3">
-        <v>13</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
@@ -2081,32 +2002,27 @@
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="A29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C25:C26)</f>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C27)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C11,C17:C21,C27:C27)</f>
-        <v>15.4375</v>
+      <c r="B32" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C10,C16:C19,C25:C26)</f>
+        <v>16.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2139,7 +2055,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -2150,7 +2066,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -2161,7 +2077,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2172,7 +2088,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -2183,7 +2099,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -2194,7 +2110,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -2205,7 +2121,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -2216,7 +2132,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2227,7 +2143,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B10" s="1">
         <v>5</v>
@@ -2248,10 +2164,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C13" s="1">
         <f>AVERAGE(C2:C10)</f>
@@ -2261,7 +2177,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -2272,7 +2188,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
@@ -2283,7 +2199,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B18" s="2">
         <v>2</v>
@@ -2294,7 +2210,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -2305,7 +2221,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
@@ -2326,10 +2242,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C16:C20)</f>
@@ -2338,7 +2254,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
@@ -2359,10 +2275,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C26:C26)</f>
@@ -2371,10 +2287,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C10,C16:C20,C26:C26)</f>
@@ -2385,7 +2301,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C32 C13" formulaRange="1"/>
+    <ignoredError sqref="C13 C32" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
